--- a/Uploads/1_new_701.xlsx
+++ b/Uploads/1_new_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,22 +37,7 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>نسكويك علبة- 77 جم</t>
-  </si>
-  <si>
-    <t>صابون ديتول الاصلى - 60 جم</t>
-  </si>
-  <si>
-    <t>صابون ديتول عناية بالبشرة - 60 جم</t>
-  </si>
-  <si>
-    <t>ديتول صابون كوول- 60 جم</t>
-  </si>
-  <si>
-    <t>صابون ديتول جدد نشاطك - 60 جم</t>
-  </si>
-  <si>
-    <t>عصير جهينة اورينتال خروب - 1 لتر</t>
+    <t>اد مى كاتشب حار سكويز - 425 جم</t>
   </si>
   <si>
     <t>YES</t>
@@ -413,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,104 +426,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>207</v>
+        <v>25906</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>142</v>
+        <v>465</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>1198</v>
-      </c>
-      <c r="B3" t="s">
         <v>8</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>156</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>1199</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>186</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>1200</v>
-      </c>
-      <c r="B5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>186</v>
-      </c>
-      <c r="E5" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>1201</v>
-      </c>
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>186</v>
-      </c>
-      <c r="E6" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>10605</v>
-      </c>
-      <c r="B7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>531</v>
-      </c>
-      <c r="E7" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_701.xlsx
+++ b/Uploads/1_new_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
   <si>
     <t>Product ID</t>
   </si>
@@ -40,10 +40,31 @@
     <t>فاين بيبي كبير مقاس4 عبوة اقتصادية- 58 حفاضة</t>
   </si>
   <si>
+    <t>فاين بيبي اصفر وسط مقاس3- 58 حفاضة</t>
+  </si>
+  <si>
     <t>فاين بيبى اصفر ماكسي مقاس5- 84 حفاضة</t>
   </si>
   <si>
+    <t>فاين بيبى حفاضات دبل لوك صغير مقاس 2 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك وسط مقاس 3 - 58 حفاضة</t>
+  </si>
+  <si>
+    <t>فاين بيبى حفاضات دبل لوك كبير مقاس 4 - 58 حفاضة</t>
+  </si>
+  <si>
     <t>حفاضات فاين بيبى مقاس 2 دبل لوك - 84 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى مقاس 3 دبل لوك - 80 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
+  </si>
+  <si>
+    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
   </si>
   <si>
     <t>YES</t>
@@ -404,7 +425,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -441,10 +462,10 @@
         <v>2</v>
       </c>
       <c r="D2">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -458,15 +479,15 @@
         <v>25</v>
       </c>
       <c r="D3">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>1682</v>
+        <v>891</v>
       </c>
       <c r="B4" t="s">
         <v>8</v>
@@ -475,15 +496,15 @@
         <v>2</v>
       </c>
       <c r="D4">
-        <v>342</v>
+        <v>356</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>1682</v>
+        <v>891</v>
       </c>
       <c r="B5" t="s">
         <v>8</v>
@@ -492,44 +513,265 @@
         <v>25</v>
       </c>
       <c r="D5">
-        <v>171</v>
+        <v>119</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>13256</v>
+        <v>1682</v>
       </c>
       <c r="B6" t="s">
         <v>9</v>
       </c>
       <c r="C6">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D6">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>13256</v>
+        <v>1682</v>
       </c>
       <c r="B7" t="s">
         <v>9</v>
       </c>
       <c r="C7">
+        <v>25</v>
+      </c>
+      <c r="D7">
+        <v>174</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>9207</v>
+      </c>
+      <c r="B8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8">
+        <v>25</v>
+      </c>
+      <c r="D8">
+        <v>253</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>9207</v>
+      </c>
+      <c r="B9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9">
         <v>29</v>
       </c>
-      <c r="D7">
-        <v>688</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
+      <c r="D9">
+        <v>760</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>9208</v>
+      </c>
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10">
+        <v>25</v>
+      </c>
+      <c r="D10">
+        <v>297</v>
+      </c>
+      <c r="E10" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>9208</v>
+      </c>
+      <c r="B11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11">
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>890</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>9209</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>297</v>
+      </c>
+      <c r="E12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>9209</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13">
+        <v>29</v>
+      </c>
+      <c r="D13">
+        <v>890</v>
+      </c>
+      <c r="E13" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>13256</v>
+      </c>
+      <c r="B14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C14">
+        <v>25</v>
+      </c>
+      <c r="D14">
+        <v>351</v>
+      </c>
+      <c r="E14" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>13256</v>
+      </c>
+      <c r="B15" t="s">
+        <v>13</v>
+      </c>
+      <c r="C15">
+        <v>29</v>
+      </c>
+      <c r="D15">
+        <v>703</v>
+      </c>
+      <c r="E15" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>13257</v>
+      </c>
+      <c r="B16" t="s">
+        <v>14</v>
+      </c>
+      <c r="C16">
+        <v>25</v>
+      </c>
+      <c r="D16">
+        <v>374</v>
+      </c>
+      <c r="E16" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17">
+        <v>13257</v>
+      </c>
+      <c r="B17" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17">
+        <v>29</v>
+      </c>
+      <c r="D17">
+        <v>749</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18">
+        <v>13258</v>
+      </c>
+      <c r="B18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18">
+        <v>25</v>
+      </c>
+      <c r="D18">
+        <v>374</v>
+      </c>
+      <c r="E18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>13258</v>
+      </c>
+      <c r="B19" t="s">
+        <v>15</v>
+      </c>
+      <c r="C19">
+        <v>29</v>
+      </c>
+      <c r="D19">
+        <v>749</v>
+      </c>
+      <c r="E19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>13259</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20">
+        <v>29</v>
+      </c>
+      <c r="D20">
+        <v>835</v>
+      </c>
+      <c r="E20" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>

--- a/Uploads/1_new_701.xlsx
+++ b/Uploads/1_new_701.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="65">
   <si>
     <t>Product ID</t>
   </si>
@@ -37,34 +37,175 @@
     <t>Tags</t>
   </si>
   <si>
-    <t>فاين بيبي كبير مقاس4 عبوة اقتصادية- 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبي اصفر وسط مقاس3- 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبى اصفر ماكسي مقاس5- 84 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبى حفاضات دبل لوك صغير مقاس 2 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبى حفاضات دبل لوك وسط مقاس 3 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>فاين بيبى حفاضات دبل لوك كبير مقاس 4 - 58 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى مقاس 2 دبل لوك - 84 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى مقاس 3 دبل لوك - 80 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى ماكسى مقاس 4 دبل لوك - 80 حفاضة</t>
-  </si>
-  <si>
-    <t>حفاضات فاين بيبى كبير مقاس 5 دبل لوك - 76 حفاضة</t>
+    <t>%تايجر اكسلانس فلفل حلو تايلاندي زياده 15 - 20 جنية</t>
+  </si>
+  <si>
+    <t>حفاضات بى بم مقاس 5 - 35 حفاضة</t>
+  </si>
+  <si>
+    <t>حلواني حلاوة طحينية سادة - 280 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة حار 170 جم + 30 جم - 200 جم</t>
+  </si>
+  <si>
+    <t>جاجوار كريشين كونز ليمون والتوابل - 10 جنية</t>
+  </si>
+  <si>
+    <t>حلواني حلاوة طحينية سادة - 575 جم</t>
+  </si>
+  <si>
+    <t>عسل البوادى اسود - 190 جم</t>
+  </si>
+  <si>
+    <t>اولويز ماكسى سميكة فردى ملمس قطنى طويل - 8 فوطة</t>
+  </si>
+  <si>
+    <t>تونة دولفين قطعة واحدة بارد - 200 جم</t>
+  </si>
+  <si>
+    <t>حفاضات بى بم مقاس 3 - 35 حفاضة</t>
+  </si>
+  <si>
+    <t>ثمرات صلصة - 200 جم</t>
+  </si>
+  <si>
+    <t>جاجوار كريشين ستريبس بالشطة المولعة - 10 جنية</t>
+  </si>
+  <si>
+    <t>ثمرات برغل - 500 جم</t>
+  </si>
+  <si>
+    <t>بقسماط ناعم ريتش بيك - 10 كيلو</t>
+  </si>
+  <si>
+    <t>ثمرات ذرة فشار - 500 جم</t>
+  </si>
+  <si>
+    <t>حفاضات بى بم مقاس 1 - 35 حفاضة</t>
+  </si>
+  <si>
+    <t>%تايجر ويفز بطعم طماطم مخللة وجبنة كريمي زياده 15 - 20 جنية</t>
+  </si>
+  <si>
+    <t>ثمرات حمص  - 500 جم</t>
+  </si>
+  <si>
+    <t>سردين دولفين بارد - 125 جم</t>
+  </si>
+  <si>
+    <t>صلصة هارفست صفيح - 375 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة بارد - 140 جم</t>
+  </si>
+  <si>
+    <t>ثمرات فاصوليا بيضاء - 500 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين جولد فصوص حار - 170 جم</t>
+  </si>
+  <si>
+    <t>طحينة البوادى - 240 جم</t>
+  </si>
+  <si>
+    <t>ثمرات صلصة - 260 جم</t>
+  </si>
+  <si>
+    <t>ثمرات لوبيا بيضاء - 500 جم</t>
+  </si>
+  <si>
+    <t>اولويز ماكسى سميكة طويل جدا نعومة قطنية - 7 فوطة</t>
+  </si>
+  <si>
+    <t>تونة دولفين قطع 140 جم + 10 جم - 150 جم</t>
+  </si>
+  <si>
+    <t>ثمرات خل - 900 مل</t>
+  </si>
+  <si>
+    <t>ثمرات زيت خليط -. 1.7 لتر</t>
+  </si>
+  <si>
+    <t>حفاضات بى بم مقاس 4 - 35 حفاضة</t>
+  </si>
+  <si>
+    <t>ثمرات ترمس - 500 جم</t>
+  </si>
+  <si>
+    <t>ثمرات فول استرالى مجروش - 500 جم</t>
+  </si>
+  <si>
+    <t>%تايجر ويفي بطعم كاتشب هالبينو زياده 15 - 20 جنية</t>
+  </si>
+  <si>
+    <t>طحينة الرشيدى الميزان - 130 جم</t>
+  </si>
+  <si>
+    <t>تونة دولفين قطع بارد - 185 جم</t>
+  </si>
+  <si>
+    <t>%بيج شيبس كيتل كوكد بطعم ريتش تشيز زياده 15 - 20 جنية</t>
+  </si>
+  <si>
+    <t>تونة دولفين مفتتة بارد 170 جم + 30 جم - 200 جم</t>
+  </si>
+  <si>
+    <t>طحينة البوادى - 125 جم</t>
+  </si>
+  <si>
+    <t>ثمرات فول استرالى - 500 جم</t>
+  </si>
+  <si>
+    <t>ثمرات فول بلدى تدميس - 500 جم</t>
+  </si>
+  <si>
+    <t>ثمرات عدس اصفر - 500 جم</t>
+  </si>
+  <si>
+    <t>مولبد ماكسى مضغوطة حماية ضد البكتيريا طويل جدا فردى - 7 فوطة</t>
+  </si>
+  <si>
+    <t>جاجوار كريشين تورتيلا فلفل حلو التايلاندى - 10 جنية</t>
+  </si>
+  <si>
+    <t>ثمرات صلصة - 360 جم</t>
+  </si>
+  <si>
+    <t>التمساح عسل اسود - 330 جم</t>
+  </si>
+  <si>
+    <t>بيج كولا ميكس توت - 200 مل</t>
+  </si>
+  <si>
+    <t>البوادي حلاوه سبريد شيكولاته بالبندق- 160 جم</t>
+  </si>
+  <si>
+    <t>عسل البوادى اسود - 680 جم</t>
+  </si>
+  <si>
+    <t>%تايجر اكسلانس جبنة مدخنة زياده 15 - 20 جنية</t>
+  </si>
+  <si>
+    <t>ثمرات عدس بجبة - 500 جم</t>
+  </si>
+  <si>
+    <t>%تايجر اكسلانس بارميزان ترافل زياده 15 - 20 جنية</t>
+  </si>
+  <si>
+    <t>توليدو تونة قطعه واحدة- 185 جم</t>
+  </si>
+  <si>
+    <t>%تايجر اكسلانس ويفي بطعم سموكد سالمون زياده 15 - 20 جنية</t>
+  </si>
+  <si>
+    <t>مولبد ماكسى طويل مضغوطة حماية ضد البكتيريا - 8 فوطة</t>
+  </si>
+  <si>
+    <t>بقسماط ناعم ريتش بيك - 25 كيلو</t>
+  </si>
+  <si>
+    <t>%تايجر اكسلانس ليمون حلو زياده 15 - 20 جنية</t>
   </si>
   <si>
     <t>YES</t>
@@ -425,7 +566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -453,325 +594,1039 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>488</v>
+        <v>20574</v>
       </c>
       <c r="B2" t="s">
         <v>7</v>
       </c>
       <c r="C2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>351</v>
+        <v>181.5</v>
       </c>
       <c r="E2" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>488</v>
+        <v>25995</v>
       </c>
       <c r="B3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D3">
-        <v>117</v>
+        <v>190.75</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>891</v>
+        <v>948</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>356</v>
+        <v>683</v>
       </c>
       <c r="E4" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>891</v>
+        <v>2859</v>
       </c>
       <c r="B5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C5">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D5">
-        <v>119</v>
+        <v>824.75</v>
       </c>
       <c r="E5" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>1682</v>
+        <v>25995</v>
       </c>
       <c r="B6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="D6">
-        <v>349</v>
+        <v>953.5</v>
       </c>
       <c r="E6" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>1682</v>
+        <v>13908</v>
       </c>
       <c r="B7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C7">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D7">
-        <v>174</v>
+        <v>89.25</v>
       </c>
       <c r="E7" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>9207</v>
+        <v>3915</v>
       </c>
       <c r="B8" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C8">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D8">
-        <v>253</v>
+        <v>466</v>
       </c>
       <c r="E8" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>9207</v>
+        <v>2103</v>
       </c>
       <c r="B9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="C9">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="D9">
-        <v>760</v>
+        <v>355.75</v>
       </c>
       <c r="E9" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>9208</v>
+        <v>2216</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D10">
-        <v>297</v>
+        <v>190.75</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>9208</v>
+        <v>947</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C11">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="D11">
-        <v>890</v>
+        <v>1413.75</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>9209</v>
+        <v>25993</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C12">
-        <v>25</v>
+        <v>80</v>
       </c>
       <c r="D12">
-        <v>297</v>
+        <v>173.25</v>
       </c>
       <c r="E12" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>9209</v>
+        <v>25875</v>
       </c>
       <c r="B13" t="s">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="C13">
-        <v>29</v>
+        <v>2</v>
       </c>
       <c r="D13">
-        <v>890</v>
+        <v>179.5</v>
       </c>
       <c r="E13" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>13256</v>
+        <v>13913</v>
       </c>
       <c r="B14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="C14">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="D14">
-        <v>351</v>
+        <v>89.25</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>13256</v>
+        <v>25993</v>
       </c>
       <c r="B15" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C15">
         <v>29</v>
       </c>
       <c r="D15">
-        <v>703</v>
+        <v>866.75</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>13257</v>
+        <v>25861</v>
       </c>
       <c r="B16" t="s">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="C16">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D16">
-        <v>374</v>
+        <v>205.25</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>13257</v>
+        <v>26065</v>
       </c>
       <c r="B17" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>29</v>
+        <v>137</v>
       </c>
       <c r="D17">
-        <v>749</v>
+        <v>455.5</v>
       </c>
       <c r="E17" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>13258</v>
+        <v>25866</v>
       </c>
       <c r="B18" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="C18">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="D18">
-        <v>374</v>
+        <v>221</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>13258</v>
+        <v>25991</v>
       </c>
       <c r="B19" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C19">
         <v>29</v>
       </c>
       <c r="D19">
-        <v>749</v>
+        <v>736.75</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>13259</v>
+        <v>23111</v>
       </c>
       <c r="B20" t="s">
+        <v>23</v>
+      </c>
+      <c r="C20">
+        <v>1</v>
+      </c>
+      <c r="D20">
+        <v>181.5</v>
+      </c>
+      <c r="E20" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21">
+        <v>25844</v>
+      </c>
+      <c r="B21" t="s">
+        <v>24</v>
+      </c>
+      <c r="C21">
+        <v>2</v>
+      </c>
+      <c r="D21">
+        <v>352.75</v>
+      </c>
+      <c r="E21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22">
+        <v>1409</v>
+      </c>
+      <c r="B22" t="s">
+        <v>25</v>
+      </c>
+      <c r="C22">
         <v>16</v>
       </c>
-      <c r="C20">
+      <c r="D22">
+        <v>1369.75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23">
+        <v>66</v>
+      </c>
+      <c r="B23" t="s">
+        <v>26</v>
+      </c>
+      <c r="C23">
+        <v>15</v>
+      </c>
+      <c r="D23">
+        <v>195.25</v>
+      </c>
+      <c r="E23" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24">
+        <v>1413</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24">
+        <v>1153.5</v>
+      </c>
+      <c r="E24" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25">
+        <v>25857</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25">
+        <v>2</v>
+      </c>
+      <c r="D25">
+        <v>310.5</v>
+      </c>
+      <c r="E25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26">
+        <v>9877</v>
+      </c>
+      <c r="B26" t="s">
         <v>29</v>
       </c>
-      <c r="D20">
-        <v>835</v>
-      </c>
-      <c r="E20" t="s">
-        <v>17</v>
+      <c r="C26">
+        <v>1</v>
+      </c>
+      <c r="D26">
+        <v>2962.75</v>
+      </c>
+      <c r="E26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27">
+        <v>590</v>
+      </c>
+      <c r="B27" t="s">
+        <v>30</v>
+      </c>
+      <c r="C27">
+        <v>1</v>
+      </c>
+      <c r="D27">
+        <v>1213</v>
+      </c>
+      <c r="E27" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28">
+        <v>25874</v>
+      </c>
+      <c r="B28" t="s">
+        <v>31</v>
+      </c>
+      <c r="C28">
+        <v>2</v>
+      </c>
+      <c r="D28">
+        <v>206</v>
+      </c>
+      <c r="E28" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29">
+        <v>25859</v>
+      </c>
+      <c r="B29" t="s">
+        <v>32</v>
+      </c>
+      <c r="C29">
+        <v>2</v>
+      </c>
+      <c r="D29">
+        <v>294.75</v>
+      </c>
+      <c r="E29" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30">
+        <v>2217</v>
+      </c>
+      <c r="B30" t="s">
+        <v>33</v>
+      </c>
+      <c r="C30">
+        <v>1</v>
+      </c>
+      <c r="D30">
+        <v>384.5</v>
+      </c>
+      <c r="E30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31">
+        <v>3429</v>
+      </c>
+      <c r="B31" t="s">
+        <v>34</v>
+      </c>
+      <c r="C31">
+        <v>16</v>
+      </c>
+      <c r="D31">
+        <v>1088</v>
+      </c>
+      <c r="E31" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32">
+        <v>25876</v>
+      </c>
+      <c r="B32" t="s">
+        <v>35</v>
+      </c>
+      <c r="C32">
+        <v>1</v>
+      </c>
+      <c r="D32">
+        <v>154.75</v>
+      </c>
+      <c r="E32" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33">
+        <v>26553</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33">
+        <v>479</v>
+      </c>
+      <c r="E33" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34">
+        <v>25994</v>
+      </c>
+      <c r="B34" t="s">
+        <v>37</v>
+      </c>
+      <c r="C34">
+        <v>29</v>
+      </c>
+      <c r="D34">
+        <v>866.75</v>
+      </c>
+      <c r="E34" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35">
+        <v>25860</v>
+      </c>
+      <c r="B35" t="s">
+        <v>38</v>
+      </c>
+      <c r="C35">
+        <v>2</v>
+      </c>
+      <c r="D35">
+        <v>236.75</v>
+      </c>
+      <c r="E35" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36">
+        <v>25850</v>
+      </c>
+      <c r="B36" t="s">
+        <v>39</v>
+      </c>
+      <c r="C36">
+        <v>2</v>
+      </c>
+      <c r="D36">
+        <v>205.25</v>
+      </c>
+      <c r="E36" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37">
+        <v>23112</v>
+      </c>
+      <c r="B37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C37">
+        <v>1</v>
+      </c>
+      <c r="D37">
+        <v>181.5</v>
+      </c>
+      <c r="E37" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38">
+        <v>964</v>
+      </c>
+      <c r="B38" t="s">
+        <v>41</v>
+      </c>
+      <c r="C38">
+        <v>15</v>
+      </c>
+      <c r="D38">
+        <v>263</v>
+      </c>
+      <c r="E38" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39">
+        <v>944</v>
+      </c>
+      <c r="B39" t="s">
+        <v>42</v>
+      </c>
+      <c r="C39">
+        <v>16</v>
+      </c>
+      <c r="D39">
+        <v>1337.25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40">
+        <v>24735</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40">
+        <v>181.5</v>
+      </c>
+      <c r="E40" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41">
+        <v>3430</v>
+      </c>
+      <c r="B41" t="s">
+        <v>44</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41">
+        <v>1638.75</v>
+      </c>
+      <c r="E41" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42">
+        <v>336</v>
+      </c>
+      <c r="B42" t="s">
+        <v>45</v>
+      </c>
+      <c r="C42">
+        <v>15</v>
+      </c>
+      <c r="D42">
+        <v>267.25</v>
+      </c>
+      <c r="E42" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43">
+        <v>25852</v>
+      </c>
+      <c r="B43" t="s">
+        <v>46</v>
+      </c>
+      <c r="C43">
+        <v>2</v>
+      </c>
+      <c r="D43">
+        <v>184.25</v>
+      </c>
+      <c r="E43" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44">
+        <v>25848</v>
+      </c>
+      <c r="B44" t="s">
+        <v>47</v>
+      </c>
+      <c r="C44">
+        <v>2</v>
+      </c>
+      <c r="D44">
+        <v>379</v>
+      </c>
+      <c r="E44" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45">
+        <v>25991</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45">
+        <v>80</v>
+      </c>
+      <c r="D45">
+        <v>147.25</v>
+      </c>
+      <c r="E45" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46">
+        <v>25856</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46">
+        <v>2</v>
+      </c>
+      <c r="D46">
+        <v>258</v>
+      </c>
+      <c r="E46" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47">
+        <v>9122</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47">
+        <v>1</v>
+      </c>
+      <c r="D47">
+        <v>418.5</v>
+      </c>
+      <c r="E47" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48">
+        <v>13909</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48">
+        <v>1</v>
+      </c>
+      <c r="D48">
+        <v>89.25</v>
+      </c>
+      <c r="E48" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49">
+        <v>25873</v>
+      </c>
+      <c r="B49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49">
+        <v>2</v>
+      </c>
+      <c r="D49">
+        <v>243</v>
+      </c>
+      <c r="E49" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50">
+        <v>4673</v>
+      </c>
+      <c r="B50" t="s">
+        <v>52</v>
+      </c>
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50">
+        <v>538.75</v>
+      </c>
+      <c r="E50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51">
+        <v>26190</v>
+      </c>
+      <c r="B51" t="s">
+        <v>53</v>
+      </c>
+      <c r="C51">
+        <v>2</v>
+      </c>
+      <c r="D51">
+        <v>135</v>
+      </c>
+      <c r="E51" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52">
+        <v>5341</v>
+      </c>
+      <c r="B52" t="s">
+        <v>54</v>
+      </c>
+      <c r="C52">
+        <v>15</v>
+      </c>
+      <c r="D52">
+        <v>88.25</v>
+      </c>
+      <c r="E52" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53">
+        <v>70</v>
+      </c>
+      <c r="B53" t="s">
+        <v>55</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53">
+        <v>522.25</v>
+      </c>
+      <c r="E53" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54">
+        <v>20575</v>
+      </c>
+      <c r="B54" t="s">
+        <v>56</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54">
+        <v>181.5</v>
+      </c>
+      <c r="E54" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55">
+        <v>25854</v>
+      </c>
+      <c r="B55" t="s">
+        <v>57</v>
+      </c>
+      <c r="C55">
+        <v>2</v>
+      </c>
+      <c r="D55">
+        <v>247.25</v>
+      </c>
+      <c r="E55" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56">
+        <v>20582</v>
+      </c>
+      <c r="B56" t="s">
+        <v>58</v>
+      </c>
+      <c r="C56">
+        <v>1</v>
+      </c>
+      <c r="D56">
+        <v>181.5</v>
+      </c>
+      <c r="E56" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57">
+        <v>2480</v>
+      </c>
+      <c r="B57" t="s">
+        <v>59</v>
+      </c>
+      <c r="C57">
+        <v>1</v>
+      </c>
+      <c r="D57">
+        <v>2799.25</v>
+      </c>
+      <c r="E57" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58">
+        <v>22658</v>
+      </c>
+      <c r="B58" t="s">
+        <v>60</v>
+      </c>
+      <c r="C58">
+        <v>1</v>
+      </c>
+      <c r="D58">
+        <v>181.5</v>
+      </c>
+      <c r="E58" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59">
+        <v>25994</v>
+      </c>
+      <c r="B59" t="s">
+        <v>37</v>
+      </c>
+      <c r="C59">
+        <v>80</v>
+      </c>
+      <c r="D59">
+        <v>173.25</v>
+      </c>
+      <c r="E59" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60">
+        <v>12463</v>
+      </c>
+      <c r="B60" t="s">
+        <v>61</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="D60">
+        <v>416.75</v>
+      </c>
+      <c r="E60" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61">
+        <v>26064</v>
+      </c>
+      <c r="B61" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61">
+        <v>137</v>
+      </c>
+      <c r="D61">
+        <v>1139</v>
+      </c>
+      <c r="E61" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62">
+        <v>25538</v>
+      </c>
+      <c r="B62" t="s">
+        <v>63</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62">
+        <v>181.5</v>
+      </c>
+      <c r="E62" t="s">
+        <v>64</v>
       </c>
     </row>
   </sheetData>
